--- a/model_maker_web_v2/results/Senergy/Senergy_stage2.xlsx
+++ b/model_maker_web_v2/results/Senergy/Senergy_stage2.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -665,39 +665,27 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>INNER_TEMP</t>
+          <t>Flash / Update (펌웨어 업데이트 중)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>0x101C</t>
+          <t>0x0006</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>S16</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>°C 1</t>
-        </is>
-      </c>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Inner Temperature</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -705,22 +693,22 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Total Energy</t>
+          <t>INNER_TEMP</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>0x1021</t>
+          <t>0x101C</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>kWh</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -730,10 +718,14 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>cumulative_energy</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Inner Temperature</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -741,12 +733,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Total generation time</t>
+          <t>Total Energy</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>0x1023</t>
+          <t>0x1021</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -754,13 +746,21 @@
           <t>U32</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>cumulative_energy</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
@@ -769,17 +769,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Decimals of total energy</t>
+          <t>Total generation time</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>0x104C</t>
+          <t>0x1023</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
@@ -788,16 +788,8 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>cumulative_energy_low</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Wh</t>
-        </is>
-      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -805,29 +797,37 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Device Model name</t>
+          <t>Decimals of total energy</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>0x1A00</t>
+          <t>0x104C</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>STRINGING</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Wh</t>
+        </is>
+      </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>cumulative_energy_low</t>
+        </is>
+      </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Ex.：PV 30KTL</t>
+          <t>Relate to 0x1021, if total energy is 220.836kWh, then 0x104C is 836Wh</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Device Serial number</t>
+          <t>Device Model name</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>0x1A10</t>
+          <t>0x1A00</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -859,7 +859,7 @@
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Ex.：1234-123456789</t>
+          <t>Ex.：PV 30KTL</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Master firmware version</t>
+          <t>Device Serial number</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>0x1A1C</t>
+          <t>0x1A10</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -891,7 +891,7 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Ex.：123456</t>
+          <t>Ex.：1234-123456789</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Slave firmware version</t>
+          <t>Master firmware version</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>0x1A26</t>
+          <t>0x1A1C</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>MPPT_COUNT</t>
+          <t>Slave firmware version</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>0x1A3B</t>
+          <t>0x1A26</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>STRINGING</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
@@ -955,7 +955,7 @@
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>MPPT Number | Ex.：1=1 MPPT</t>
+          <t>Ex.：123456</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Nominal Voltage</t>
+          <t>MPPT_COUNT</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>0x1A44</t>
+          <t>0x1A3B</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Ex.：2200 = 220V</t>
+          <t>MPPT Number | Ex.：1=1 MPPT</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Nominal Frequency</t>
+          <t>Nominal Voltage</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>0x1A45</t>
+          <t>0x1A44</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1010,7 +1010,11 @@
           <t>U16</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>V 0.1</t>
+        </is>
+      </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1019,7 +1023,7 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Ex.：5000 = 50Hz</t>
+          <t>Ex.：2200 = 220VFor CN (NB/T 32004) regulation code (0x5101=0x0E), the unit is 10ms. Other regulation codes use 1ms.</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1033,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Nominal Active Power(Low word)</t>
+          <t>Nominal Frequency</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>0x1A46</t>
+          <t>0x1A45</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1044,7 +1048,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>Hz 0.01</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1055,7 +1059,7 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Ex.：1500 = 1500W</t>
+          <t>Ex.：5000 = 50HzOnly support for 3 phase model (0x1A48 = 3).</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1069,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Grid Phase Number</t>
+          <t>Nominal Active Power (Low word)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>0x1A48</t>
+          <t>0x1A46</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1078,7 +1082,11 @@
           <t>U16</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>W 1</t>
+        </is>
+      </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1087,7 +1095,7 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>1=single phase2=split phase3=three phases</t>
+          <t>Ex.：1500 = 1500W</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1105,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Nominal Active Power(High word)</t>
+          <t>Grid Phase Number</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>0x1A4E</t>
+          <t>0x1A48</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1110,11 +1118,7 @@
           <t>U16</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>W 1</t>
-        </is>
-      </c>
+      <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1123,7 +1127,7 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Ex.：1 = (1*65536)W</t>
+          <t>1=single phase2=split phase3=three phases</t>
         </is>
       </c>
     </row>
@@ -1133,20 +1137,24 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>EMS Firmware Version</t>
+          <t>Nominal Active Power (High word)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>0x1A60</t>
+          <t>0x1A4E</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>STRINGING</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr"/>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>W 1</t>
+        </is>
+      </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1155,7 +1163,7 @@
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Ex.：123456</t>
+          <t>Ex.：1 = (1*65536)W</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1173,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>LCD firmware version</t>
+          <t>EMS Firmware Version</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>0x1A8E</t>
+          <t>0x1A60</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1191,95 +1199,99 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>H01 MONITORING (168개)</t>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>LCD firmware version</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0x1A8E</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>STRINGING</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Ex.：123456</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>H01 MONITORING (173개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Unit/Scale</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>R/W</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>H01 Field</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Broadcast address</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>0x0000</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Start bit</t>
+          <t>Wait / Initial (대기/초기화)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>0x0001</t>
+          <t>0x0000</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1298,16 +1310,16 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Register number</t>
+          <t>Standby (스탠바이)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>0x0002</t>
+          <t>0x0001</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1326,16 +1338,16 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Read register address</t>
+          <t>Initialization (초기화 중)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>0x0003</t>
+          <t>0x0002</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1354,21 +1366,21 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>PV string reverse</t>
+          <t>On-Grid / Normal (정상 발전 / 계통 연계)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>0x0005</t>
+          <t>0x0003</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
@@ -1382,16 +1394,16 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>0x07</t>
+          <t>Grid over current, [0,1]</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>0x0007</t>
+          <t>0x0008</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1410,16 +1422,16 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Dc-link over voltage</t>
+          <t>EN50438 (유럽 공통)</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>0x0009</t>
+          <t>0x000A</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1438,11 +1450,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Software incompatibility</t>
+          <t>Self control(outage), [0,1]</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1466,16 +1478,16 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Data inconsistency</t>
+          <t>Leakage current abnormal, [0,1]</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000C</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1494,11 +1506,11 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Byte number</t>
+          <t>Register value</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1522,7 +1534,7 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
@@ -1558,7 +1570,7 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
@@ -1594,7 +1606,7 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
@@ -1662,7 +1674,7 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
@@ -1698,7 +1710,7 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
@@ -1734,7 +1746,7 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1778,7 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
@@ -1802,7 +1814,7 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
@@ -1838,7 +1850,7 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
@@ -1874,7 +1886,7 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
@@ -1906,7 +1918,7 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
@@ -1942,7 +1954,7 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
@@ -1978,7 +1990,7 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
@@ -2014,7 +2026,7 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
@@ -2050,7 +2062,7 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
@@ -2086,7 +2098,7 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
@@ -2122,7 +2134,7 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
@@ -2158,7 +2170,7 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
@@ -2194,7 +2206,7 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
@@ -2230,7 +2242,7 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
@@ -2266,7 +2278,7 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
@@ -2302,7 +2314,7 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
@@ -2338,7 +2350,7 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2367,11 @@
           <t>S32</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr"/>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
           <t>RO</t>
@@ -2370,7 +2386,7 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
@@ -2402,7 +2418,7 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
@@ -2419,7 +2435,11 @@
           <t>S16</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr"/>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
           <t>RO</t>
@@ -2434,7 +2454,7 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
@@ -2470,7 +2490,7 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
@@ -2506,7 +2526,7 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
@@ -2542,7 +2562,7 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
@@ -2578,7 +2598,7 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
@@ -2614,7 +2634,7 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
@@ -2650,7 +2670,7 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
@@ -2686,7 +2706,7 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
@@ -2722,7 +2742,7 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
@@ -2758,7 +2778,7 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
@@ -2794,7 +2814,7 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
@@ -2830,7 +2850,7 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
@@ -2866,7 +2886,7 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
@@ -2902,7 +2922,7 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
@@ -2938,7 +2958,7 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
@@ -2974,7 +2994,7 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
@@ -3010,7 +3030,7 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
@@ -3046,7 +3066,7 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
@@ -3082,7 +3102,7 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
@@ -3118,7 +3138,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
@@ -3154,7 +3174,7 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
@@ -3190,7 +3210,7 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
@@ -3226,7 +3246,7 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
@@ -3262,7 +3282,7 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
@@ -3298,7 +3318,7 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
@@ -3334,7 +3354,7 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
@@ -3370,7 +3390,7 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
@@ -3406,7 +3426,7 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
@@ -3442,7 +3462,7 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
@@ -3478,7 +3498,7 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
@@ -3514,7 +3534,7 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
@@ -3550,7 +3570,7 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
@@ -3586,7 +3606,7 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
@@ -3622,7 +3642,7 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
@@ -3658,7 +3678,7 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
@@ -3694,7 +3714,7 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
@@ -3730,7 +3750,7 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
@@ -3766,7 +3786,7 @@
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
@@ -3802,7 +3822,7 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
@@ -3838,7 +3858,7 @@
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
@@ -3874,7 +3894,7 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
@@ -3910,7 +3930,7 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
@@ -3946,7 +3966,7 @@
     </row>
     <row r="114">
       <c r="A114" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
@@ -3982,7 +4002,7 @@
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
@@ -4018,7 +4038,7 @@
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
@@ -4054,7 +4074,7 @@
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
@@ -4090,7 +4110,7 @@
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
@@ -4126,7 +4146,7 @@
     </row>
     <row r="119">
       <c r="A119" s="6" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
@@ -4162,7 +4182,7 @@
     </row>
     <row r="120">
       <c r="A120" s="6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
@@ -4198,7 +4218,7 @@
     </row>
     <row r="121">
       <c r="A121" s="6" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
@@ -4234,7 +4254,7 @@
     </row>
     <row r="122">
       <c r="A122" s="6" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
@@ -4270,7 +4290,7 @@
     </row>
     <row r="123">
       <c r="A123" s="6" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
@@ -4306,7 +4326,7 @@
     </row>
     <row r="124">
       <c r="A124" s="6" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
@@ -4342,7 +4362,7 @@
     </row>
     <row r="125">
       <c r="A125" s="6" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
@@ -4378,7 +4398,7 @@
     </row>
     <row r="126">
       <c r="A126" s="6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
@@ -4414,11 +4434,11 @@
     </row>
     <row r="127">
       <c r="A127" s="6" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>External fan speed dutypercentage</t>
+          <t>External fan speed duty percentage</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -4431,7 +4451,11 @@
           <t>U16</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr"/>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
           <t>RO</t>
@@ -4442,24 +4466,28 @@
     </row>
     <row r="128">
       <c r="A128" s="6" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Q (Reference Output reactivepower)</t>
+          <t>L1-N phase voltage (AC)</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>0x1226</t>
+          <t>0x1220</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>S16</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr"/>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>V 0.1</t>
+        </is>
+      </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
           <t>RO</t>
@@ -4470,26 +4498,26 @@
     </row>
     <row r="129">
       <c r="A129" s="6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>L1 watt of grid</t>
+          <t>L2-N phase voltage (AC)</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>0x1300</t>
+          <t>0x1221</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
@@ -4502,26 +4530,26 @@
     </row>
     <row r="130">
       <c r="A130" s="6" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>L2 watt of grid</t>
+          <t>L3-N phase voltage (AC)</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>0x1302</t>
+          <t>0x1222</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
@@ -4534,26 +4562,26 @@
     </row>
     <row r="131">
       <c r="A131" s="6" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>L3 watt of grid</t>
+          <t>L1-L2 phase voltage (AC)</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>0x1304</t>
+          <t>0x1223</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
@@ -4566,26 +4594,26 @@
     </row>
     <row r="132">
       <c r="A132" s="6" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Accumulated energy ofimport</t>
+          <t>L2-L3 phase voltage (AC)</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>0x1306</t>
+          <t>0x1224</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
@@ -4593,35 +4621,31 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>cumulative_energy</t>
-        </is>
-      </c>
+      <c r="G132" s="6" t="inlineStr"/>
       <c r="H132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Accumulated energy ofexport</t>
+          <t>L3-L1 phase voltage (AC)</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>0x1308</t>
+          <t>0x1225</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
@@ -4629,35 +4653,31 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G133" s="6" t="inlineStr">
-        <is>
-          <t>cumulative_energy</t>
-        </is>
-      </c>
+      <c r="G133" s="6" t="inlineStr"/>
       <c r="H133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>L1 watt of load</t>
+          <t>Q (Reference Output reactive power)</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>0x130A</t>
+          <t>0x1226</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
@@ -4670,21 +4690,21 @@
     </row>
     <row r="135">
       <c r="A135" s="6" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>L2 watt of load</t>
+          <t>L1 watt of grid</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>0x130C</t>
+          <t>0x1300</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4702,21 +4722,21 @@
     </row>
     <row r="136">
       <c r="A136" s="6" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>L3 watt of load</t>
+          <t>L2 watt of grid</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>0x130E</t>
+          <t>0x1302</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4734,26 +4754,26 @@
     </row>
     <row r="137">
       <c r="A137" s="6" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Accumulated energy of load</t>
+          <t>L3 watt of grid</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>0x1310</t>
+          <t>0x1304</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
@@ -4761,35 +4781,31 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G137" s="6" t="inlineStr">
-        <is>
-          <t>cumulative_energy</t>
-        </is>
-      </c>
+      <c r="G137" s="6" t="inlineStr"/>
       <c r="H137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>L1-N phase voltage of grid</t>
+          <t>Accumulated energy of import</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>0x131A</t>
+          <t>0x1306</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>Wh 10</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
@@ -4797,31 +4813,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G138" s="6" t="inlineStr"/>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>cumulative_energy</t>
+        </is>
+      </c>
       <c r="H138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>L2-N phase voltage of grid</t>
+          <t>Accumulated energy of export</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>0x131B</t>
+          <t>0x1308</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>Wh 10</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
@@ -4829,31 +4849,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G139" s="6" t="inlineStr"/>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>cumulative_energy</t>
+        </is>
+      </c>
       <c r="H139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>L3-N phase voltage of grid</t>
+          <t>L1 watt of load</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>0x131C</t>
+          <t>0x130A</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
@@ -4866,26 +4890,26 @@
     </row>
     <row r="141">
       <c r="A141" s="6" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>L1 current of grid</t>
+          <t>L2 watt of load</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>0x131D</t>
+          <t>0x130C</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
@@ -4898,26 +4922,26 @@
     </row>
     <row r="142">
       <c r="A142" s="6" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>L2 current of grid</t>
+          <t>L3 watt of load</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>0x131F</t>
+          <t>0x130E</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
@@ -4930,26 +4954,26 @@
     </row>
     <row r="143">
       <c r="A143" s="6" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>L3 current of grid</t>
+          <t>Accumulated energy of load</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>0x1321</t>
+          <t>0x1310</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>Wh 10</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
@@ -4957,21 +4981,25 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G143" s="6" t="inlineStr"/>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>cumulative_energy</t>
+        </is>
+      </c>
       <c r="H143" s="6" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>L1-N phase voltage of load</t>
+          <t>L1-N phase voltage of grid</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>0x1323</t>
+          <t>0x131A</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -4994,16 +5022,16 @@
     </row>
     <row r="145">
       <c r="A145" s="6" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>L2-N phase voltage of load</t>
+          <t>L2-N phase voltage of grid</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>0x1324</t>
+          <t>0x131B</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
@@ -5026,16 +5054,16 @@
     </row>
     <row r="146">
       <c r="A146" s="6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>L3-N phase voltage of load</t>
+          <t>L3-N phase voltage of grid</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>0x1325</t>
+          <t>0x131C</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
@@ -5058,16 +5086,16 @@
     </row>
     <row r="147">
       <c r="A147" s="6" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>L1 current of load</t>
+          <t>L1 current of grid</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>0x1326</t>
+          <t>0x131D</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -5090,16 +5118,16 @@
     </row>
     <row r="148">
       <c r="A148" s="6" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>L2 current of load</t>
+          <t>L2 current of grid</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>0x1328</t>
+          <t>0x131F</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -5122,16 +5150,16 @@
     </row>
     <row r="149">
       <c r="A149" s="6" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>L3 current of load</t>
+          <t>L3 current of grid</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>0x132A</t>
+          <t>0x1321</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
@@ -5154,26 +5182,26 @@
     </row>
     <row r="150">
       <c r="A150" s="6" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Today import Energy</t>
+          <t>L1-N phase voltage of load</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>0x1332</t>
+          <t>0x1323</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
@@ -5186,26 +5214,26 @@
     </row>
     <row r="151">
       <c r="A151" s="6" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Today export Energy</t>
+          <t>L2-N phase voltage of load</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>0x1334</t>
+          <t>0x1324</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
@@ -5218,26 +5246,26 @@
     </row>
     <row r="152">
       <c r="A152" s="6" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Today load Energy</t>
+          <t>L3-N phase voltage of load</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>0x1336</t>
+          <t>0x1325</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
@@ -5250,26 +5278,26 @@
     </row>
     <row r="153">
       <c r="A153" s="6" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Frequency of grid</t>
+          <t>L1 current of load</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>0x1338</t>
+          <t>0x1326</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>Hz 0.01</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
@@ -5282,27 +5310,31 @@
     </row>
     <row r="154">
       <c r="A154" s="6" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Power flow direction</t>
+          <t>L2 current of load</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>0x30B2</t>
+          <t>0x1328</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="inlineStr"/>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr"/>
@@ -5310,27 +5342,31 @@
     </row>
     <row r="155">
       <c r="A155" s="6" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Maximum feed in grid power</t>
+          <t>L3 current of load</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>0x30B9</t>
+          <t>0x132A</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>U32</t>
-        </is>
-      </c>
-      <c r="E155" s="6" t="inlineStr"/>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr"/>
@@ -5338,27 +5374,31 @@
     </row>
     <row r="156">
       <c r="A156" s="6" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Clear the EEPROM historyenergy record</t>
+          <t>Today import Energy</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>0x6009</t>
+          <t>0x1332</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E156" s="6" t="inlineStr"/>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>Wh 10</t>
+        </is>
+      </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr"/>
@@ -5366,26 +5406,26 @@
     </row>
     <row r="157">
       <c r="A157" s="6" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Tracker 1 voltage</t>
+          <t>Today export Energy</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>0x8000</t>
+          <t>0x1334</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>Wh 10</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
@@ -5398,26 +5438,26 @@
     </row>
     <row r="158">
       <c r="A158" s="6" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>String 1-1 current</t>
+          <t>Today load Energy</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>0x8040</t>
+          <t>0x1336</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>Wh 10</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
@@ -5425,35 +5465,31 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G158" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G158" s="6" t="inlineStr"/>
       <c r="H158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>String 1-2 current</t>
+          <t>Frequency of grid</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>0x8080</t>
+          <t>0x1338</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>Hz 0.01</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr">
@@ -5461,97 +5497,81 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G159" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G159" s="6" t="inlineStr"/>
       <c r="H159" s="6" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>String 1-3 current</t>
+          <t>Power flow direction</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>0x80C0</t>
+          <t>0x30B2</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>A 0.01</t>
-        </is>
-      </c>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr"/>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
       <c r="H160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>String 1-4 current</t>
+          <t>Maximum feed in grid power</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>0x8100</t>
+          <t>0x30B9</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr"/>
       <c r="H161" s="6" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Tracker 2 voltage</t>
+          <t>Clear the EEPROM history energy record</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>0x8140</t>
+          <t>0x6009</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
@@ -5559,14 +5579,10 @@
           <t>U16</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>V 0.1</t>
-        </is>
-      </c>
+      <c r="E162" s="6" t="inlineStr"/>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr"/>
@@ -5574,26 +5590,26 @@
     </row>
     <row r="163">
       <c r="A163" s="6" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>String 2-1 current</t>
+          <t>Tracker 1 voltage</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>0x8180</t>
+          <t>0x8000</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
@@ -5601,30 +5617,26 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G163" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G163" s="6" t="inlineStr"/>
       <c r="H163" s="6" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>String 2-2 current</t>
+          <t>String 1-1 current</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>0x81C0</t>
+          <t>0x8040</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -5646,21 +5658,21 @@
     </row>
     <row r="165">
       <c r="A165" s="6" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>String 2-3 current</t>
+          <t>String 1-2 current</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>0x8200</t>
+          <t>0x8080</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
@@ -5682,21 +5694,21 @@
     </row>
     <row r="166">
       <c r="A166" s="6" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>String 2-4 current</t>
+          <t>String 1-3 current</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>0x8240</t>
+          <t>0x80C0</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -5718,26 +5730,26 @@
     </row>
     <row r="167">
       <c r="A167" s="6" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>Tracker 3 voltage</t>
+          <t>String 1-4 current</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>0x8280</t>
+          <t>0x8100</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
@@ -5745,31 +5757,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G167" s="6" t="inlineStr"/>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
       <c r="H167" s="6" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>String 3-1 current</t>
+          <t>Tracker 2 voltage</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>0x82C0</t>
+          <t>0x8140</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
@@ -5777,30 +5793,26 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G168" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G168" s="6" t="inlineStr"/>
       <c r="H168" s="6" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>String 3-2 current</t>
+          <t>String 2-1 current</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>0x8300</t>
+          <t>0x8180</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
@@ -5822,21 +5834,21 @@
     </row>
     <row r="170">
       <c r="A170" s="6" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>String 3-3 current</t>
+          <t>String 2-2 current</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>0x8340</t>
+          <t>0x81C0</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -5858,21 +5870,21 @@
     </row>
     <row r="171">
       <c r="A171" s="6" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>String 3-4 current</t>
+          <t>String 2-3 current</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>0x8380</t>
+          <t>0x8200</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -5894,26 +5906,26 @@
     </row>
     <row r="172">
       <c r="A172" s="6" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Tracker 4 voltage</t>
+          <t>String 2-4 current</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>0x83C0</t>
+          <t>0x8240</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
@@ -5921,31 +5933,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G172" s="6" t="inlineStr"/>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
       <c r="H172" s="6" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>String 4-1 current</t>
+          <t>Tracker 3 voltage</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>0x8400</t>
+          <t>0x8280</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F173" s="6" t="inlineStr">
@@ -5953,30 +5969,26 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G173" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G173" s="6" t="inlineStr"/>
       <c r="H173" s="6" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>String 4-2 current</t>
+          <t>String 3-1 current</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>0x8440</t>
+          <t>0x82C0</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -5998,21 +6010,21 @@
     </row>
     <row r="175">
       <c r="A175" s="6" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>String 4-3 current</t>
+          <t>String 3-2 current</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>0x8480</t>
+          <t>0x8300</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
@@ -6034,21 +6046,21 @@
     </row>
     <row r="176">
       <c r="A176" s="6" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>String 4-4 current</t>
+          <t>String 3-3 current</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>0x84C0</t>
+          <t>0x8340</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -6070,26 +6082,26 @@
     </row>
     <row r="177">
       <c r="A177" s="6" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>Tracker 5 voltage</t>
+          <t>String 3-4 current</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>0x8500</t>
+          <t>0x8380</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="F177" s="6" t="inlineStr">
@@ -6097,31 +6109,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G177" s="6" t="inlineStr"/>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
       <c r="H177" s="6" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>String 5-1 current</t>
+          <t>Tracker 4 voltage</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>0x8540</t>
+          <t>0x83C0</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
@@ -6129,30 +6145,26 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G178" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G178" s="6" t="inlineStr"/>
       <c r="H178" s="6" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>String 5-2 current</t>
+          <t>String 4-1 current</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>0x8580</t>
+          <t>0x8400</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
@@ -6174,21 +6186,21 @@
     </row>
     <row r="180">
       <c r="A180" s="6" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>String 5-3 current</t>
+          <t>String 4-2 current</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>0x85C0</t>
+          <t>0x8440</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -6210,21 +6222,21 @@
     </row>
     <row r="181">
       <c r="A181" s="6" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>String 5-4 current</t>
+          <t>String 4-3 current</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>0x8600</t>
+          <t>0x8480</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -6246,26 +6258,26 @@
     </row>
     <row r="182">
       <c r="A182" s="6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Tracker 6 voltage</t>
+          <t>String 4-4 current</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>0x8640</t>
+          <t>0x84C0</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
@@ -6273,31 +6285,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G182" s="6" t="inlineStr"/>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
       <c r="H182" s="6" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>String 6-1 current</t>
+          <t>Tracker 5 voltage</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>0x8680</t>
+          <t>0x8500</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
@@ -6305,30 +6321,26 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G183" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G183" s="6" t="inlineStr"/>
       <c r="H183" s="6" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>String 6-2 current</t>
+          <t>String 5-1 current</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>0x86C0</t>
+          <t>0x8540</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -6350,21 +6362,21 @@
     </row>
     <row r="185">
       <c r="A185" s="6" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>String 6-3 current</t>
+          <t>String 5-2 current</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>0x8700</t>
+          <t>0x8580</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
@@ -6386,21 +6398,21 @@
     </row>
     <row r="186">
       <c r="A186" s="6" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>String 6-4 current</t>
+          <t>String 5-3 current</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>0x8740</t>
+          <t>0x85C0</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -6422,26 +6434,26 @@
     </row>
     <row r="187">
       <c r="A187" s="6" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>Tracker 7 voltage</t>
+          <t>String 5-4 current</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>0x8780</t>
+          <t>0x8600</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="F187" s="6" t="inlineStr">
@@ -6449,31 +6461,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G187" s="6" t="inlineStr"/>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
       <c r="H187" s="6" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>String 7-1 current</t>
+          <t>Tracker 6 voltage</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>0x87C0</t>
+          <t>0x8640</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
@@ -6481,30 +6497,26 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G188" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G188" s="6" t="inlineStr"/>
       <c r="H188" s="6" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>String 7-2 current</t>
+          <t>String 6-1 current</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>0x8800</t>
+          <t>0x8680</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
@@ -6526,21 +6538,21 @@
     </row>
     <row r="190">
       <c r="A190" s="6" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>String 7-3 current</t>
+          <t>String 6-2 current</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>0x8840</t>
+          <t>0x86C0</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -6562,21 +6574,21 @@
     </row>
     <row r="191">
       <c r="A191" s="6" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>String 7-4 current</t>
+          <t>String 6-3 current</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>0x8880</t>
+          <t>0x8700</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
@@ -6598,26 +6610,26 @@
     </row>
     <row r="192">
       <c r="A192" s="6" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Tracker 8 voltage</t>
+          <t>String 6-4 current</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>0x88C0</t>
+          <t>0x8740</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
@@ -6625,31 +6637,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G192" s="6" t="inlineStr"/>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
       <c r="H192" s="6" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>String 8-1 current</t>
+          <t>Tracker 7 voltage</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>0x8900</t>
+          <t>0x8780</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F193" s="6" t="inlineStr">
@@ -6657,30 +6673,26 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G193" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G193" s="6" t="inlineStr"/>
       <c r="H193" s="6" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>String 8-2 current</t>
+          <t>String 7-1 current</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>0x8940</t>
+          <t>0x87C0</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -6702,21 +6714,21 @@
     </row>
     <row r="195">
       <c r="A195" s="6" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>String 8-3 current</t>
+          <t>String 7-2 current</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>0x8980</t>
+          <t>0x8800</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
@@ -6738,21 +6750,21 @@
     </row>
     <row r="196">
       <c r="A196" s="6" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>String 8-4 current</t>
+          <t>String 7-3 current</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>0x89C0</t>
+          <t>0x8840</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -6774,26 +6786,26 @@
     </row>
     <row r="197">
       <c r="A197" s="6" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>Tracker 9 voltage</t>
+          <t>String 7-4 current</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>0x8A00</t>
+          <t>0x8880</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="F197" s="6" t="inlineStr">
@@ -6801,31 +6813,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G197" s="6" t="inlineStr"/>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
       <c r="H197" s="6" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>String 9-1 current</t>
+          <t>Tracker 8 voltage</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>0x8A40</t>
+          <t>0x88C0</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
@@ -6833,30 +6849,26 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="G198" s="6" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="G198" s="6" t="inlineStr"/>
       <c r="H198" s="6" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>String 9-2 current</t>
+          <t>String 8-1 current</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>0x8A80</t>
+          <t>0x8900</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
@@ -6878,21 +6890,21 @@
     </row>
     <row r="200">
       <c r="A200" s="6" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>String 9-3 current</t>
+          <t>String 8-2 current</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>0x8AC0</t>
+          <t>0x8940</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -6914,21 +6926,21 @@
     </row>
     <row r="201">
       <c r="A201" s="6" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>String 9-4 current</t>
+          <t>String 8-3 current</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>0x8B00</t>
+          <t>0x8980</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -6950,44 +6962,52 @@
     </row>
     <row r="202">
       <c r="A202" s="6" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>history log 0</t>
+          <t>String 8-4 current</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>0xB600</t>
+          <t>0x89C0</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E202" s="6" t="inlineStr"/>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="G202" s="6" t="inlineStr"/>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
       <c r="H202" s="6" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>history log 127</t>
+          <t>Tracker 9 voltage</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>0xB77D</t>
+          <t>0x8A00</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
@@ -6995,7 +7015,11 @@
           <t>U16</t>
         </is>
       </c>
-      <c r="E203" s="6" t="inlineStr"/>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>V 0.1</t>
+        </is>
+      </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
           <t>RO</t>
@@ -7004,475 +7028,655 @@
       <c r="G203" s="6" t="inlineStr"/>
       <c r="H203" s="6" t="inlineStr"/>
     </row>
+    <row r="204">
+      <c r="A204" s="6" t="n">
+        <v>168</v>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>String 9-1 current</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>0x8A40</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="n">
+        <v>169</v>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>String 9-2 current</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>0x8A80</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr"/>
+    </row>
     <row r="206">
-      <c r="A206" s="3" t="inlineStr">
+      <c r="A206" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>String 9-3 current</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>0x8AC0</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="n">
+        <v>171</v>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>String 9-4 current</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>0x8B00</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="n">
+        <v>172</v>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>history log 0</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>0xB600</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr"/>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr"/>
+      <c r="H208" s="6" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>history log 127</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>0xB77D</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr"/>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr"/>
+      <c r="H209" s="6" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
         <is>
           <t>STATUS 레지스터</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="4" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B207" s="4" t="inlineStr">
+      <c r="B213" s="4" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr">
+      <c r="C213" s="4" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="D207" s="4" t="inlineStr">
+      <c r="D213" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E207" s="4" t="inlineStr">
+      <c r="E213" s="4" t="inlineStr">
         <is>
           <t>Unit/Scale</t>
         </is>
       </c>
-      <c r="F207" s="4" t="inlineStr">
+      <c r="F213" s="4" t="inlineStr">
         <is>
           <t>R/W</t>
         </is>
       </c>
-      <c r="G207" s="4" t="inlineStr">
+      <c r="G213" s="4" t="inlineStr">
         <is>
           <t>H01 Field</t>
         </is>
       </c>
-      <c r="H207" s="4" t="inlineStr">
+      <c r="H213" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="7" t="n">
+    <row r="214">
+      <c r="A214" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B208" s="7" t="inlineStr">
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>Off-Grid (독립 운전)</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="inlineStr">
+        <is>
+          <t>0x0004</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr"/>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="inlineStr"/>
+      <c r="H214" s="7" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>Derating (출력 제한 운전 중)</t>
+        </is>
+      </c>
+      <c r="C215" s="7" t="inlineStr">
+        <is>
+          <t>0x0007</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr"/>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="inlineStr"/>
+      <c r="H215" s="7" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>Shutdown mode</t>
+        </is>
+      </c>
+      <c r="C216" s="7" t="inlineStr">
+        <is>
+          <t>0x0009</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr"/>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr"/>
+      <c r="H216" s="7" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
         <is>
           <t>Inverter Mode</t>
         </is>
       </c>
-      <c r="C208" s="7" t="inlineStr">
+      <c r="C217" s="7" t="inlineStr">
         <is>
           <t>0x101D</t>
         </is>
       </c>
-      <c r="D208" s="7" t="inlineStr">
+      <c r="D217" s="7" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="E208" s="7" t="inlineStr"/>
-      <c r="F208" s="7" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G208" s="7" t="inlineStr">
+      <c r="E217" s="7" t="inlineStr"/>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
         <is>
           <t>inverter_status</t>
         </is>
       </c>
-      <c r="H208" s="7" t="inlineStr">
+      <c r="H217" s="7" t="inlineStr">
         <is>
           <t>Inverter Mode Table</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="7" t="n">
+    <row r="218">
+      <c r="A218" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t>DER-AVM digital meter connect status</t>
+        </is>
+      </c>
+      <c r="C218" s="7" t="inlineStr">
+        <is>
+          <t>0x1210</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr"/>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="inlineStr"/>
+      <c r="H218" s="7" t="inlineStr">
+        <is>
+          <t>0: disconnected1: connected</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>DER-AVM mode</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="inlineStr">
+        <is>
+          <t>0x1211</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr"/>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr"/>
+      <c r="H219" s="7" t="inlineStr">
+        <is>
+          <t>0: self control1: DER-AVM control</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>ALARM 레지스터</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>Unit/Scale</t>
+        </is>
+      </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>H01 Field</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
+          <t>Fault / Alarm (고장 발생)</t>
+        </is>
+      </c>
+      <c r="C224" s="8" t="inlineStr">
+        <is>
+          <t>0x0005</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E224" s="8" t="inlineStr"/>
+      <c r="F224" s="8" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G224" s="8" t="inlineStr"/>
+      <c r="H224" s="8" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B209" s="7" t="inlineStr">
-        <is>
-          <t>DER-AVM digital meterconnect status</t>
-        </is>
-      </c>
-      <c r="C209" s="7" t="inlineStr">
-        <is>
-          <t>0x1210</t>
-        </is>
-      </c>
-      <c r="D209" s="7" t="inlineStr">
+      <c r="B225" s="8" t="inlineStr">
+        <is>
+          <t>Error Code1</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>0x101E</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="E209" s="7" t="inlineStr"/>
-      <c r="F209" s="7" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G209" s="7" t="inlineStr"/>
-      <c r="H209" s="7" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="7" t="n">
+      <c r="E225" s="8" t="inlineStr"/>
+      <c r="F225" s="8" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G225" s="8" t="inlineStr">
+        <is>
+          <t>alarm1</t>
+        </is>
+      </c>
+      <c r="H225" s="8" t="inlineStr">
+        <is>
+          <t>Error Code Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B210" s="7" t="inlineStr">
-        <is>
-          <t>DER-AVM mode</t>
-        </is>
-      </c>
-      <c r="C210" s="7" t="inlineStr">
-        <is>
-          <t>0x1211</t>
-        </is>
-      </c>
-      <c r="D210" s="7" t="inlineStr">
+      <c r="B226" s="8" t="inlineStr">
+        <is>
+          <t>Error Code2</t>
+        </is>
+      </c>
+      <c r="C226" s="8" t="inlineStr">
+        <is>
+          <t>0x101F</t>
+        </is>
+      </c>
+      <c r="D226" s="8" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="E210" s="7" t="inlineStr"/>
-      <c r="F210" s="7" t="inlineStr">
+      <c r="E226" s="8" t="inlineStr"/>
+      <c r="F226" s="8" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G226" s="8" t="inlineStr">
+        <is>
+          <t>alarm2</t>
+        </is>
+      </c>
+      <c r="H226" s="8" t="inlineStr">
+        <is>
+          <t>Error Code Table 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>Error Code3</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>0x1020</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E227" s="8" t="inlineStr"/>
+      <c r="F227" s="8" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G227" s="8" t="inlineStr">
+        <is>
+          <t>alarm3</t>
+        </is>
+      </c>
+      <c r="H227" s="8" t="inlineStr">
+        <is>
+          <t>Error Code Table 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B228" s="8" t="inlineStr">
+        <is>
+          <t>EEPROM default</t>
+        </is>
+      </c>
+      <c r="C228" s="8" t="inlineStr">
+        <is>
+          <t>0x6006</t>
+        </is>
+      </c>
+      <c r="D228" s="8" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="E228" s="8" t="inlineStr"/>
+      <c r="F228" s="8" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="G210" s="7" t="inlineStr"/>
-      <c r="H210" s="7" t="inlineStr">
-        <is>
-          <t>0: self control1: DER-AVM control</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>ALARM 레지스터</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B214" s="4" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="D214" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>Unit/Scale</t>
-        </is>
-      </c>
-      <c r="F214" s="4" t="inlineStr">
-        <is>
-          <t>R/W</t>
-        </is>
-      </c>
-      <c r="G214" s="4" t="inlineStr">
-        <is>
-          <t>H01 Field</t>
-        </is>
-      </c>
-      <c r="H214" s="4" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B215" s="8" t="inlineStr">
-        <is>
-          <t>GFCI abnormal</t>
-        </is>
-      </c>
-      <c r="C215" s="8" t="inlineStr">
-        <is>
-          <t>0x0004</t>
-        </is>
-      </c>
-      <c r="D215" s="8" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E215" s="8" t="inlineStr"/>
-      <c r="F215" s="8" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G215" s="8" t="inlineStr"/>
-      <c r="H215" s="8" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B216" s="8" t="inlineStr">
-        <is>
-          <t>Internal communication error</t>
-        </is>
-      </c>
-      <c r="C216" s="8" t="inlineStr">
-        <is>
-          <t>0x000A</t>
-        </is>
-      </c>
-      <c r="D216" s="8" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E216" s="8" t="inlineStr"/>
-      <c r="F216" s="8" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G216" s="8" t="inlineStr"/>
-      <c r="H216" s="8" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B217" s="8" t="inlineStr">
-        <is>
-          <t>Internal storage error</t>
-        </is>
-      </c>
-      <c r="C217" s="8" t="inlineStr">
-        <is>
-          <t>0x000C</t>
-        </is>
-      </c>
-      <c r="D217" s="8" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E217" s="8" t="inlineStr"/>
-      <c r="F217" s="8" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G217" s="8" t="inlineStr"/>
-      <c r="H217" s="8" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B218" s="8" t="inlineStr">
-        <is>
-          <t>Inverter abnormal</t>
-        </is>
-      </c>
-      <c r="C218" s="8" t="inlineStr">
-        <is>
-          <t>0x000E</t>
-        </is>
-      </c>
-      <c r="D218" s="8" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E218" s="8" t="inlineStr"/>
-      <c r="F218" s="8" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G218" s="8" t="inlineStr"/>
-      <c r="H218" s="8" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B219" s="8" t="inlineStr">
-        <is>
-          <t>Boost abnormal</t>
-        </is>
-      </c>
-      <c r="C219" s="8" t="inlineStr">
-        <is>
-          <t>0x000F</t>
-        </is>
-      </c>
-      <c r="D219" s="8" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E219" s="8" t="inlineStr"/>
-      <c r="F219" s="8" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G219" s="8" t="inlineStr"/>
-      <c r="H219" s="8" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B220" s="8" t="inlineStr">
-        <is>
-          <t>Error Code1</t>
-        </is>
-      </c>
-      <c r="C220" s="8" t="inlineStr">
-        <is>
-          <t>0x101E</t>
-        </is>
-      </c>
-      <c r="D220" s="8" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E220" s="8" t="inlineStr"/>
-      <c r="F220" s="8" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G220" s="8" t="inlineStr">
-        <is>
-          <t>alarm1</t>
-        </is>
-      </c>
-      <c r="H220" s="8" t="inlineStr">
-        <is>
-          <t>Error Code Table 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B221" s="8" t="inlineStr">
-        <is>
-          <t>Error Code2</t>
-        </is>
-      </c>
-      <c r="C221" s="8" t="inlineStr">
-        <is>
-          <t>0x101F</t>
-        </is>
-      </c>
-      <c r="D221" s="8" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E221" s="8" t="inlineStr"/>
-      <c r="F221" s="8" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G221" s="8" t="inlineStr">
-        <is>
-          <t>alarm2</t>
-        </is>
-      </c>
-      <c r="H221" s="8" t="inlineStr">
-        <is>
-          <t>Error Code Table 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B222" s="8" t="inlineStr">
-        <is>
-          <t>Error Code3</t>
-        </is>
-      </c>
-      <c r="C222" s="8" t="inlineStr">
-        <is>
-          <t>0x1020</t>
-        </is>
-      </c>
-      <c r="D222" s="8" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E222" s="8" t="inlineStr"/>
-      <c r="F222" s="8" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="G222" s="8" t="inlineStr">
-        <is>
-          <t>alarm3</t>
-        </is>
-      </c>
-      <c r="H222" s="8" t="inlineStr">
-        <is>
-          <t>Error Code Table 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B223" s="8" t="inlineStr">
-        <is>
-          <t>EEPROM default</t>
-        </is>
-      </c>
-      <c r="C223" s="8" t="inlineStr">
-        <is>
-          <t>0x6006</t>
-        </is>
-      </c>
-      <c r="D223" s="8" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="E223" s="8" t="inlineStr"/>
-      <c r="F223" s="8" t="inlineStr">
-        <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="G223" s="8" t="inlineStr"/>
-      <c r="H223" s="8" t="inlineStr"/>
+      <c r="G228" s="8" t="inlineStr"/>
+      <c r="H228" s="8" t="inlineStr">
+        <is>
+          <t>[0, 1]0: EEPROM setting NOT to default1: EEPROM setting to default</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7608,7 +7812,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7854,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -7660,7 +7864,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17">
@@ -7670,7 +7874,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -7680,7 +7884,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -8108,7 +8312,7 @@
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>Accumulated energy ofimport</t>
+          <t>Accumulated energy of import</t>
         </is>
       </c>
     </row>
